--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R501"/>
+  <dimension ref="A1:R502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30453,7 +30453,7 @@
         <v>296.24</v>
       </c>
       <c r="C501" t="n">
-        <v>285.38</v>
+        <v>285.25</v>
       </c>
       <c r="D501" t="n">
         <v>299.69</v>
@@ -30471,7 +30471,7 @@
         <v>286.31</v>
       </c>
       <c r="I501" t="n">
-        <v>257.73</v>
+        <v>257.79</v>
       </c>
       <c r="J501" t="n">
         <v>247.35</v>
@@ -30500,6 +30500,66 @@
       <c r="R501" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>294.58</v>
+      </c>
+      <c r="C502" t="n">
+        <v>282.68</v>
+      </c>
+      <c r="D502" t="n">
+        <v>294.18</v>
+      </c>
+      <c r="E502" t="n">
+        <v>299.45</v>
+      </c>
+      <c r="F502" t="n">
+        <v>292.67</v>
+      </c>
+      <c r="G502" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="H502" t="n">
+        <v>285.82</v>
+      </c>
+      <c r="I502" t="n">
+        <v>256.17</v>
+      </c>
+      <c r="J502" t="n">
+        <v>246.07</v>
+      </c>
+      <c r="K502" t="n">
+        <v>245.16</v>
+      </c>
+      <c r="L502" t="n">
+        <v>256.52</v>
+      </c>
+      <c r="M502" t="n">
+        <v>258.02</v>
+      </c>
+      <c r="N502" t="n">
+        <v>264.31</v>
+      </c>
+      <c r="O502" t="n">
+        <v>272.1</v>
+      </c>
+      <c r="P502" t="n">
+        <v>289.07</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>292.67</v>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30514,7 +30574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35827,6 +35887,16 @@
       </c>
       <c r="B531" t="n">
         <v>0.82</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.78</v>
       </c>
     </row>
   </sheetData>
@@ -35995,28 +36065,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003204533323642953</v>
+        <v>-0.002910806504504151</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L2" t="n">
-        <v>6.183592696440421e-06</v>
+        <v>5.124323369520845e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.925116318362869</v>
+        <v>7.910871794931554</v>
       </c>
       <c r="N2" t="n">
-        <v>95.02691306922233</v>
+        <v>94.83836531436715</v>
       </c>
       <c r="O2" t="n">
-        <v>9.748174858363095</v>
+        <v>9.738499130480381</v>
       </c>
       <c r="P2" t="n">
-        <v>293.9166634932399</v>
+        <v>293.9135248366354</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36073,28 +36143,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3176268607296164</v>
+        <v>-0.3187560779062572</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K3" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02651453715666918</v>
+        <v>0.02681075641106323</v>
       </c>
       <c r="M3" t="n">
-        <v>11.93718013583733</v>
+        <v>11.91914967912845</v>
       </c>
       <c r="N3" t="n">
-        <v>210.6476360968078</v>
+        <v>210.2397355450442</v>
       </c>
       <c r="O3" t="n">
-        <v>14.51370511264466</v>
+        <v>14.49964604895734</v>
       </c>
       <c r="P3" t="n">
-        <v>293.9977775388653</v>
+        <v>294.0099151603478</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36151,28 +36221,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5839520590207303</v>
+        <v>-0.5816147953004613</v>
       </c>
       <c r="J4" t="n">
+        <v>501</v>
+      </c>
+      <c r="K4" t="n">
         <v>500</v>
       </c>
-      <c r="K4" t="n">
-        <v>499</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.115725497142119</v>
+        <v>0.115304310872683</v>
       </c>
       <c r="M4" t="n">
-        <v>9.758086340917576</v>
+        <v>9.746936568192687</v>
       </c>
       <c r="N4" t="n">
-        <v>149.2824605298929</v>
+        <v>149.0553900418893</v>
       </c>
       <c r="O4" t="n">
-        <v>12.21812017169142</v>
+        <v>12.20882426943272</v>
       </c>
       <c r="P4" t="n">
-        <v>303.9532098256361</v>
+        <v>303.9282374527538</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36229,28 +36299,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2271948437608826</v>
+        <v>-0.2267094665033943</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07432275960975143</v>
+        <v>0.0743242229875366</v>
       </c>
       <c r="M5" t="n">
-        <v>4.230041254069881</v>
+        <v>4.223996952080885</v>
       </c>
       <c r="N5" t="n">
-        <v>36.78707849456647</v>
+        <v>36.71672791621278</v>
       </c>
       <c r="O5" t="n">
-        <v>6.065235238188744</v>
+        <v>6.059432969858878</v>
       </c>
       <c r="P5" t="n">
-        <v>304.3451463006373</v>
+        <v>304.3399597380368</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36307,28 +36377,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3038281926159596</v>
+        <v>-0.3050323100613457</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1885664671001106</v>
+        <v>0.1903260150969113</v>
       </c>
       <c r="M6" t="n">
-        <v>3.530739801297586</v>
+        <v>3.529546443017723</v>
       </c>
       <c r="N6" t="n">
-        <v>22.73030302137063</v>
+        <v>22.70386824593523</v>
       </c>
       <c r="O6" t="n">
-        <v>4.767630755560945</v>
+        <v>4.764857631234666</v>
       </c>
       <c r="P6" t="n">
-        <v>303.9689336486949</v>
+        <v>303.9818004042185</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36385,28 +36455,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3394697437194942</v>
+        <v>-0.3412312277661856</v>
       </c>
       <c r="J7" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3227740469017708</v>
+        <v>0.3253594740663291</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8571774216716</v>
+        <v>2.859553653204125</v>
       </c>
       <c r="N7" t="n">
-        <v>13.83559144194361</v>
+        <v>13.84849714134212</v>
       </c>
       <c r="O7" t="n">
-        <v>3.719622486482144</v>
+        <v>3.721356895185158</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2901806582175</v>
+        <v>303.3090032279545</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36463,28 +36533,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.454929328771822</v>
+        <v>-0.456338521087325</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4050945345183399</v>
+        <v>0.4072834195907646</v>
       </c>
       <c r="M8" t="n">
-        <v>3.200615895035688</v>
+        <v>3.200569763710319</v>
       </c>
       <c r="N8" t="n">
-        <v>17.39162032564291</v>
+        <v>17.38284055577209</v>
       </c>
       <c r="O8" t="n">
-        <v>4.170326165378784</v>
+        <v>4.16927338462856</v>
       </c>
       <c r="P8" t="n">
-        <v>301.7211529706896</v>
+        <v>301.7362110807425</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36541,28 +36611,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2900657435346767</v>
+        <v>-0.2962367113282013</v>
       </c>
       <c r="J9" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01394881283026483</v>
+        <v>0.01458230903641422</v>
       </c>
       <c r="M9" t="n">
-        <v>13.76688550690624</v>
+        <v>13.77056271899727</v>
       </c>
       <c r="N9" t="n">
-        <v>335.7569829759194</v>
+        <v>335.5720220141856</v>
       </c>
       <c r="O9" t="n">
-        <v>18.32367274800331</v>
+        <v>18.31862500337254</v>
       </c>
       <c r="P9" t="n">
-        <v>279.7085585492864</v>
+        <v>279.7751382478526</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36619,28 +36689,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3709746582695116</v>
+        <v>-0.3769422218247173</v>
       </c>
       <c r="J10" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K10" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02375542136418718</v>
+        <v>0.02457742296126009</v>
       </c>
       <c r="M10" t="n">
-        <v>13.54712905924216</v>
+        <v>13.54777557147852</v>
       </c>
       <c r="N10" t="n">
-        <v>323.6271749744747</v>
+        <v>323.4462884145409</v>
       </c>
       <c r="O10" t="n">
-        <v>17.9896407683554</v>
+        <v>17.98461254557742</v>
       </c>
       <c r="P10" t="n">
-        <v>271.3976450107505</v>
+        <v>271.4614121969415</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36697,28 +36767,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4310742877118756</v>
+        <v>-0.437406105344043</v>
       </c>
       <c r="J11" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K11" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03746957821591457</v>
+        <v>0.03862726961288365</v>
       </c>
       <c r="M11" t="n">
-        <v>12.33950299651475</v>
+        <v>12.3480416485779</v>
       </c>
       <c r="N11" t="n">
-        <v>270.9059716837775</v>
+        <v>270.87969006079</v>
       </c>
       <c r="O11" t="n">
-        <v>16.45922147866592</v>
+        <v>16.45842307333209</v>
       </c>
       <c r="P11" t="n">
-        <v>272.912192200177</v>
+        <v>272.9804132933525</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36775,28 +36845,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5804450272666356</v>
+        <v>-0.5830227008104644</v>
       </c>
       <c r="J12" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1649347682656259</v>
+        <v>0.1666433666206805</v>
       </c>
       <c r="M12" t="n">
-        <v>7.259527034972382</v>
+        <v>7.261191372658321</v>
       </c>
       <c r="N12" t="n">
-        <v>97.60924994551431</v>
+        <v>97.50119428560737</v>
       </c>
       <c r="O12" t="n">
-        <v>9.879739366274512</v>
+        <v>9.874269303883066</v>
       </c>
       <c r="P12" t="n">
-        <v>278.8073655748462</v>
+        <v>278.8349096449325</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36853,28 +36923,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2616323873612861</v>
+        <v>-0.2642610051364048</v>
       </c>
       <c r="J13" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K13" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06406420412125202</v>
+        <v>0.06544479068710374</v>
       </c>
       <c r="M13" t="n">
-        <v>5.819721545411349</v>
+        <v>5.822074014570982</v>
       </c>
       <c r="N13" t="n">
-        <v>57.22347518334578</v>
+        <v>57.19949365523823</v>
       </c>
       <c r="O13" t="n">
-        <v>7.564619962915902</v>
+        <v>7.563034685576831</v>
       </c>
       <c r="P13" t="n">
-        <v>271.8275809740948</v>
+        <v>271.8556694154729</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36931,28 +37001,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08151064345249733</v>
+        <v>0.08002931797497975</v>
       </c>
       <c r="J14" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K14" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006766591096171837</v>
+        <v>0.006549592026208084</v>
       </c>
       <c r="M14" t="n">
-        <v>5.921495339126906</v>
+        <v>5.917457401239397</v>
       </c>
       <c r="N14" t="n">
-        <v>55.80468071668724</v>
+        <v>55.72195112564323</v>
       </c>
       <c r="O14" t="n">
-        <v>7.470253055732934</v>
+        <v>7.464713733670115</v>
       </c>
       <c r="P14" t="n">
-        <v>265.9107348720996</v>
+        <v>265.9265637705539</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37009,28 +37079,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3820154640341471</v>
+        <v>0.3812079502430014</v>
       </c>
       <c r="J15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1292862569095967</v>
+        <v>0.1292860980464922</v>
       </c>
       <c r="M15" t="n">
-        <v>5.750324416181605</v>
+        <v>5.743184265383319</v>
       </c>
       <c r="N15" t="n">
-        <v>56.24002729434436</v>
+        <v>56.13628763201906</v>
       </c>
       <c r="O15" t="n">
-        <v>7.499335123485572</v>
+        <v>7.49241534033045</v>
       </c>
       <c r="P15" t="n">
-        <v>263.8570361333233</v>
+        <v>263.8656649282737</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37087,28 +37157,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.429031284823704</v>
+        <v>0.4292621604859818</v>
       </c>
       <c r="J16" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K16" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1343292811265685</v>
+        <v>0.1349640789051257</v>
       </c>
       <c r="M16" t="n">
-        <v>6.513774673987404</v>
+        <v>6.501729147347609</v>
       </c>
       <c r="N16" t="n">
-        <v>67.87667494160152</v>
+        <v>67.74188867952384</v>
       </c>
       <c r="O16" t="n">
-        <v>8.238730177739864</v>
+        <v>8.230546074199685</v>
       </c>
       <c r="P16" t="n">
-        <v>276.8910683353413</v>
+        <v>276.8886012830498</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37165,28 +37235,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3232385720028534</v>
+        <v>0.3222899361348003</v>
       </c>
       <c r="J17" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0884814297733304</v>
+        <v>0.08834546729958348</v>
       </c>
       <c r="M17" t="n">
-        <v>6.470853927837792</v>
+        <v>6.463040449259167</v>
       </c>
       <c r="N17" t="n">
-        <v>61.59143835965189</v>
+        <v>61.48025381687487</v>
       </c>
       <c r="O17" t="n">
-        <v>7.848021302191521</v>
+        <v>7.840934498953225</v>
       </c>
       <c r="P17" t="n">
-        <v>286.3771450341275</v>
+        <v>286.387281807614</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37224,7 +37294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R501"/>
+  <dimension ref="A1:R502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83200,7 +83270,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>-46.60038794953596,168.82039888961629</t>
+          <t>-46.60038695992681,168.82039979092818</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -83230,7 +83300,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>-46.59832520199393,168.81592331277938</t>
+          <t>-46.59832565872501,168.81592289678196</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -83276,6 +83346,98 @@
       <c r="R501" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-46.600766689358366,168.8211129851641</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-46.600367396113434,168.82041760916408</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-46.60014623073346,168.81955999688523</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-46.59987763810341,168.818745577886</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-46.59951731550768,168.81801470458592</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-46.599185233004626,168.8172581090839</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-46.598847744284114,168.81650643639915</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-46.598313326985206,168.8159341287095</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-46.59792772728299,168.81522627545203</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-46.59761208188957,168.814454705423</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>-46.597389835080506,168.81359806307256</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>-46.59709253091002,168.81280978330008</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>-46.59683168640472,168.81198829223055</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>-46.59658225764359,168.81115640047156</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>-46.59640270407404,168.81026085815057</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>-46.59612137648739,168.8094580166017</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R502"/>
+  <dimension ref="A1:R504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30558,6 +30558,126 @@
         <v>292.67</v>
       </c>
       <c r="R502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>292.86</v>
+      </c>
+      <c r="C503" t="n">
+        <v>279.64</v>
+      </c>
+      <c r="D503" t="n">
+        <v>294.16</v>
+      </c>
+      <c r="E503" t="n">
+        <v>299.42</v>
+      </c>
+      <c r="F503" t="n">
+        <v>293.43</v>
+      </c>
+      <c r="G503" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="H503" t="n">
+        <v>287.26</v>
+      </c>
+      <c r="I503" t="n">
+        <v>257.18</v>
+      </c>
+      <c r="J503" t="n">
+        <v>247.15</v>
+      </c>
+      <c r="K503" t="n">
+        <v>246.48</v>
+      </c>
+      <c r="L503" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="M503" t="n">
+        <v>260.75</v>
+      </c>
+      <c r="N503" t="n">
+        <v>266.86</v>
+      </c>
+      <c r="O503" t="n">
+        <v>274.44</v>
+      </c>
+      <c r="P503" t="n">
+        <v>291.67</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>295</v>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>293.76</v>
+      </c>
+      <c r="C504" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="D504" t="n">
+        <v>293.91</v>
+      </c>
+      <c r="E504" t="n">
+        <v>298.45</v>
+      </c>
+      <c r="F504" t="n">
+        <v>292.93</v>
+      </c>
+      <c r="G504" t="n">
+        <v>290.76</v>
+      </c>
+      <c r="H504" t="n">
+        <v>286.79</v>
+      </c>
+      <c r="I504" t="n">
+        <v>258.69</v>
+      </c>
+      <c r="J504" t="n">
+        <v>247.11</v>
+      </c>
+      <c r="K504" t="n">
+        <v>246.99</v>
+      </c>
+      <c r="L504" t="n">
+        <v>260.19</v>
+      </c>
+      <c r="M504" t="n">
+        <v>260.77</v>
+      </c>
+      <c r="N504" t="n">
+        <v>267.02</v>
+      </c>
+      <c r="O504" t="n">
+        <v>274.32</v>
+      </c>
+      <c r="P504" t="n">
+        <v>291.53</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>295.43</v>
+      </c>
+      <c r="R504" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30574,7 +30694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35897,6 +36017,26 @@
       </c>
       <c r="B532" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
@@ -36065,28 +36205,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.002910806504504151</v>
+        <v>-0.003313178801887679</v>
       </c>
       <c r="J2" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>5.124323369520845e-06</v>
+        <v>6.697304782199431e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.910871794931554</v>
+        <v>7.881362970804143</v>
       </c>
       <c r="N2" t="n">
-        <v>94.83836531436715</v>
+        <v>94.46314146729637</v>
       </c>
       <c r="O2" t="n">
-        <v>9.738499130480381</v>
+        <v>9.719215064360721</v>
       </c>
       <c r="P2" t="n">
-        <v>293.9135248366354</v>
+        <v>293.9178362380913</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36143,28 +36283,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3187560779062572</v>
+        <v>-0.3224924131772337</v>
       </c>
       <c r="J3" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02681075641106323</v>
+        <v>0.02764881235383576</v>
       </c>
       <c r="M3" t="n">
-        <v>11.91914967912845</v>
+        <v>11.89103494147906</v>
       </c>
       <c r="N3" t="n">
-        <v>210.2397355450442</v>
+        <v>209.4930589540064</v>
       </c>
       <c r="O3" t="n">
-        <v>14.49964604895734</v>
+        <v>14.47387504968888</v>
       </c>
       <c r="P3" t="n">
-        <v>294.0099151603478</v>
+        <v>294.0502053925712</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36221,28 +36361,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5816147953004613</v>
+        <v>-0.5770789509014858</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.115304310872683</v>
+        <v>0.1145107555269421</v>
       </c>
       <c r="M4" t="n">
-        <v>9.746936568192687</v>
+        <v>9.724157819927965</v>
       </c>
       <c r="N4" t="n">
-        <v>149.0553900418893</v>
+        <v>148.5964675983382</v>
       </c>
       <c r="O4" t="n">
-        <v>12.20882426943272</v>
+        <v>12.19001507785524</v>
       </c>
       <c r="P4" t="n">
-        <v>303.9282374527538</v>
+        <v>303.879619365563</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36299,28 +36439,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2267094665033943</v>
+        <v>-0.226143196268406</v>
       </c>
       <c r="J5" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0743242229875366</v>
+        <v>0.07457833079852116</v>
       </c>
       <c r="M5" t="n">
-        <v>4.223996952080885</v>
+        <v>4.209973308168077</v>
       </c>
       <c r="N5" t="n">
-        <v>36.71672791621278</v>
+        <v>36.57376467595714</v>
       </c>
       <c r="O5" t="n">
-        <v>6.059432969858878</v>
+        <v>6.047624713551357</v>
       </c>
       <c r="P5" t="n">
-        <v>304.3399597380368</v>
+        <v>304.333891519787</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36377,28 +36517,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3050323100613457</v>
+        <v>-0.3070004062877218</v>
       </c>
       <c r="J6" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1903260150969113</v>
+        <v>0.1935058677915317</v>
       </c>
       <c r="M6" t="n">
-        <v>3.529546443017723</v>
+        <v>3.525099820648139</v>
       </c>
       <c r="N6" t="n">
-        <v>22.70386824593523</v>
+        <v>22.63917422896523</v>
       </c>
       <c r="O6" t="n">
-        <v>4.764857631234666</v>
+        <v>4.75806412619305</v>
       </c>
       <c r="P6" t="n">
-        <v>303.9818004042185</v>
+        <v>304.0028991662632</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36455,28 +36595,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3412312277661856</v>
+        <v>-0.3437187128978739</v>
       </c>
       <c r="J7" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3253594740663291</v>
+        <v>0.3298457798519357</v>
       </c>
       <c r="M7" t="n">
-        <v>2.859553653204125</v>
+        <v>2.859687476889466</v>
       </c>
       <c r="N7" t="n">
-        <v>13.84849714134212</v>
+        <v>13.83393678589309</v>
       </c>
       <c r="O7" t="n">
-        <v>3.721356895185158</v>
+        <v>3.719400057252928</v>
       </c>
       <c r="P7" t="n">
-        <v>303.3090032279545</v>
+        <v>303.3356690508157</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36533,28 +36673,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.456338521087325</v>
+        <v>-0.458162763464345</v>
       </c>
       <c r="J8" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4072834195907646</v>
+        <v>0.4110264204342098</v>
       </c>
       <c r="M8" t="n">
-        <v>3.200569763710319</v>
+        <v>3.195992039481978</v>
       </c>
       <c r="N8" t="n">
-        <v>17.38284055577209</v>
+        <v>17.33569518376168</v>
       </c>
       <c r="O8" t="n">
-        <v>4.16927338462856</v>
+        <v>4.163615638331867</v>
       </c>
       <c r="P8" t="n">
-        <v>301.7362110807425</v>
+        <v>301.7557676592695</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36611,28 +36751,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2962367113282013</v>
+        <v>-0.3070686499457473</v>
       </c>
       <c r="J9" t="n">
+        <v>503</v>
+      </c>
+      <c r="K9" t="n">
         <v>501</v>
       </c>
-      <c r="K9" t="n">
-        <v>499</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01458230903641422</v>
+        <v>0.0157527814380769</v>
       </c>
       <c r="M9" t="n">
-        <v>13.77056271899727</v>
+        <v>13.7703023503082</v>
       </c>
       <c r="N9" t="n">
-        <v>335.5720220141856</v>
+        <v>334.9872527107098</v>
       </c>
       <c r="O9" t="n">
-        <v>18.31862500337254</v>
+        <v>18.30265698500384</v>
       </c>
       <c r="P9" t="n">
-        <v>279.7751382478526</v>
+        <v>279.8923711804</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36689,28 +36829,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3769422218247173</v>
+        <v>-0.3878803372205332</v>
       </c>
       <c r="J10" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02457742296126009</v>
+        <v>0.02614799864271589</v>
       </c>
       <c r="M10" t="n">
-        <v>13.54777557147852</v>
+        <v>13.54470245679417</v>
       </c>
       <c r="N10" t="n">
-        <v>323.4462884145409</v>
+        <v>322.9428284571266</v>
       </c>
       <c r="O10" t="n">
-        <v>17.98461254557742</v>
+        <v>17.97061013035246</v>
       </c>
       <c r="P10" t="n">
-        <v>271.4614121969415</v>
+        <v>271.5786670864645</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36767,28 +36907,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.437406105344043</v>
+        <v>-0.4486577435206476</v>
       </c>
       <c r="J11" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03862726961288365</v>
+        <v>0.04078252357152712</v>
       </c>
       <c r="M11" t="n">
-        <v>12.3480416485779</v>
+        <v>12.3571293610114</v>
       </c>
       <c r="N11" t="n">
-        <v>270.87969006079</v>
+        <v>270.6148002110315</v>
       </c>
       <c r="O11" t="n">
-        <v>16.45842307333209</v>
+        <v>16.45037386234828</v>
       </c>
       <c r="P11" t="n">
-        <v>272.9804132933525</v>
+        <v>273.1020285928259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36845,28 +36985,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5830227008104644</v>
+        <v>-0.5853929538811831</v>
       </c>
       <c r="J12" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K12" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1666433666206805</v>
+        <v>0.1689483036370925</v>
       </c>
       <c r="M12" t="n">
-        <v>7.261191372658321</v>
+        <v>7.247020923871368</v>
       </c>
       <c r="N12" t="n">
-        <v>97.50119428560737</v>
+        <v>97.15044506974547</v>
       </c>
       <c r="O12" t="n">
-        <v>9.874269303883066</v>
+        <v>9.856492533845165</v>
       </c>
       <c r="P12" t="n">
-        <v>278.8349096449325</v>
+        <v>278.8603174583205</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36923,28 +37063,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2642610051364048</v>
+        <v>-0.2673119253178646</v>
       </c>
       <c r="J13" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K13" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06544479068710374</v>
+        <v>0.06734530694159535</v>
       </c>
       <c r="M13" t="n">
-        <v>5.822074014570982</v>
+        <v>5.815074934460431</v>
       </c>
       <c r="N13" t="n">
-        <v>57.19949365523823</v>
+        <v>57.03294784478534</v>
       </c>
       <c r="O13" t="n">
-        <v>7.563034685576831</v>
+        <v>7.552016144367366</v>
       </c>
       <c r="P13" t="n">
-        <v>271.8556694154729</v>
+        <v>271.8883747329937</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37001,28 +37141,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08002931797497975</v>
+        <v>0.07913300167039257</v>
       </c>
       <c r="J14" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K14" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006549592026208084</v>
+        <v>0.006460093837905467</v>
       </c>
       <c r="M14" t="n">
-        <v>5.917457401239397</v>
+        <v>5.898603660001351</v>
       </c>
       <c r="N14" t="n">
-        <v>55.72195112564323</v>
+        <v>55.50567349454806</v>
       </c>
       <c r="O14" t="n">
-        <v>7.464713733670115</v>
+        <v>7.45021298316686</v>
       </c>
       <c r="P14" t="n">
-        <v>265.9265637705539</v>
+        <v>265.9361717903228</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37079,28 +37219,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3812079502430014</v>
+        <v>0.3813573965983865</v>
       </c>
       <c r="J15" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K15" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1292860980464922</v>
+        <v>0.1303653322101145</v>
       </c>
       <c r="M15" t="n">
-        <v>5.743184265383319</v>
+        <v>5.721067686834869</v>
       </c>
       <c r="N15" t="n">
-        <v>56.13628763201906</v>
+        <v>55.91324339174027</v>
       </c>
       <c r="O15" t="n">
-        <v>7.49241534033045</v>
+        <v>7.477515857003599</v>
       </c>
       <c r="P15" t="n">
-        <v>263.8656649282737</v>
+        <v>263.8640631598206</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37157,28 +37297,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4292621604859818</v>
+        <v>0.4316531063866372</v>
       </c>
       <c r="J16" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K16" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1349640789051257</v>
+        <v>0.137236405679954</v>
       </c>
       <c r="M16" t="n">
-        <v>6.501729147347609</v>
+        <v>6.485668225937436</v>
       </c>
       <c r="N16" t="n">
-        <v>67.74188867952384</v>
+        <v>67.50995610681726</v>
       </c>
       <c r="O16" t="n">
-        <v>8.230546074199685</v>
+        <v>8.216444249601969</v>
       </c>
       <c r="P16" t="n">
-        <v>276.8886012830498</v>
+        <v>276.862971063745</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37235,28 +37375,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3222899361348003</v>
+        <v>0.3223641553651465</v>
       </c>
       <c r="J17" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K17" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08834546729958348</v>
+        <v>0.08909162751935218</v>
       </c>
       <c r="M17" t="n">
-        <v>6.463040449259167</v>
+        <v>6.438161816282182</v>
       </c>
       <c r="N17" t="n">
-        <v>61.48025381687487</v>
+        <v>61.23601208680635</v>
       </c>
       <c r="O17" t="n">
-        <v>7.840934498953225</v>
+        <v>7.825344215228258</v>
       </c>
       <c r="P17" t="n">
-        <v>286.387281807614</v>
+        <v>286.3864852698683</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37294,7 +37434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R502"/>
+  <dimension ref="A1:R504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83441,6 +83581,190 @@
         </is>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-46.60075359601585,168.8211249101919</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-46.60034425447786,168.82043868597088</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-46.600146078486674,168.81956013554955</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-46.59987740973435,168.81874578588366</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-46.5995231008335,168.8180094352991</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-46.59919550952545,168.81724874913422</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-46.59885870585933,168.8164964524212</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-46.598321015292264,168.8159271260886</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-46.59793594841112,168.81521878749083</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-46.59762212989005,168.8144455534337</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>-46.59741465046458,168.81357546025632</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>-46.59711331179531,168.81279085508777</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>-46.596851097026004,168.81197061192574</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>-46.59660006965353,168.8111401760872</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>-46.596422495084624,168.8102428308918</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>-46.59613911219328,168.8094418613198</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.60076044718363,168.8211186703525</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.60035864187683,168.8204255823004</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.60014417540185,168.81956186885336</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.599870025801025,168.81875251114045</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.59951929469812,168.8180129019353</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-46.59919406320035,168.8172500664607</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-46.59885512812309,168.81649971108112</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-46.59833250969102,168.81591665681995</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-46.5979356439249,168.8152190648228</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-46.59762601207183,168.81444201743687</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>-46.59741777141741,168.81357261756932</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>-46.59711346403623,168.8127907164195</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>-46.59685231494723,168.81196950257285</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>-46.59659915621721,168.81114100810717</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>-46.596421429414896,168.8102438015907</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>-46.59614238530609,168.80943887987178</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R504"/>
+  <dimension ref="A1:R505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30678,6 +30678,66 @@
         <v>295.43</v>
       </c>
       <c r="R504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>289.55</v>
+      </c>
+      <c r="C505" t="n">
+        <v>276.94</v>
+      </c>
+      <c r="D505" t="n">
+        <v>291.77</v>
+      </c>
+      <c r="E505" t="n">
+        <v>296.16</v>
+      </c>
+      <c r="F505" t="n">
+        <v>291.12</v>
+      </c>
+      <c r="G505" t="n">
+        <v>289.72</v>
+      </c>
+      <c r="H505" t="n">
+        <v>285.89</v>
+      </c>
+      <c r="I505" t="n">
+        <v>256.59</v>
+      </c>
+      <c r="J505" t="n">
+        <v>244.17</v>
+      </c>
+      <c r="K505" t="n">
+        <v>245.49</v>
+      </c>
+      <c r="L505" t="n">
+        <v>260.26</v>
+      </c>
+      <c r="M505" t="n">
+        <v>260.97</v>
+      </c>
+      <c r="N505" t="n">
+        <v>266.91</v>
+      </c>
+      <c r="O505" t="n">
+        <v>274.56</v>
+      </c>
+      <c r="P505" t="n">
+        <v>291.84</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>295.65</v>
+      </c>
+      <c r="R505" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30694,7 +30754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36037,6 +36097,16 @@
       </c>
       <c r="B534" t="n">
         <v>0.22</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -36205,28 +36275,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003313178801887679</v>
+        <v>-0.004966457894145673</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>6.697304782199431e-06</v>
+        <v>1.51089495514789e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.881362970804143</v>
+        <v>7.873654921837909</v>
       </c>
       <c r="N2" t="n">
-        <v>94.46314146729637</v>
+        <v>94.31173030390342</v>
       </c>
       <c r="O2" t="n">
-        <v>9.719215064360721</v>
+        <v>9.711422671468039</v>
       </c>
       <c r="P2" t="n">
-        <v>293.9178362380913</v>
+        <v>293.9356013229261</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36283,28 +36353,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3224924131772337</v>
+        <v>-0.3257488079947055</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02764881235383576</v>
+        <v>0.02829622915699948</v>
       </c>
       <c r="M3" t="n">
-        <v>11.89103494147906</v>
+        <v>11.88447944612725</v>
       </c>
       <c r="N3" t="n">
-        <v>209.4930589540064</v>
+        <v>209.2135760154634</v>
       </c>
       <c r="O3" t="n">
-        <v>14.47387504968888</v>
+        <v>14.46421708961337</v>
       </c>
       <c r="P3" t="n">
-        <v>294.0502053925712</v>
+        <v>294.0854074188696</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36361,28 +36431,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5770789509014858</v>
+        <v>-0.5757047836042097</v>
       </c>
       <c r="J4" t="n">
+        <v>504</v>
+      </c>
+      <c r="K4" t="n">
         <v>503</v>
       </c>
-      <c r="K4" t="n">
-        <v>502</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1145107555269421</v>
+        <v>0.1144534402888912</v>
       </c>
       <c r="M4" t="n">
-        <v>9.724157819927965</v>
+        <v>9.709652572071562</v>
       </c>
       <c r="N4" t="n">
-        <v>148.5964675983382</v>
+        <v>148.3259812023409</v>
       </c>
       <c r="O4" t="n">
-        <v>12.19001507785524</v>
+        <v>12.17891543620945</v>
       </c>
       <c r="P4" t="n">
-        <v>303.879619365563</v>
+        <v>303.8648548267245</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36439,28 +36509,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.226143196268406</v>
+        <v>-0.2269323948870452</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07457833079852116</v>
+        <v>0.07534926065890191</v>
       </c>
       <c r="M5" t="n">
-        <v>4.209973308168077</v>
+        <v>4.205831390359227</v>
       </c>
       <c r="N5" t="n">
-        <v>36.57376467595714</v>
+        <v>36.50940445140001</v>
       </c>
       <c r="O5" t="n">
-        <v>6.047624713551357</v>
+        <v>6.042301254604905</v>
       </c>
       <c r="P5" t="n">
-        <v>304.333891519787</v>
+        <v>304.3423717458282</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36517,28 +36587,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3070004062877218</v>
+        <v>-0.3087610550907686</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1935058677915317</v>
+        <v>0.1957010411134684</v>
       </c>
       <c r="M6" t="n">
-        <v>3.525099820648139</v>
+        <v>3.526723545129483</v>
       </c>
       <c r="N6" t="n">
-        <v>22.63917422896523</v>
+        <v>22.6351008099064</v>
       </c>
       <c r="O6" t="n">
-        <v>4.75806412619305</v>
+        <v>4.75763605269533</v>
       </c>
       <c r="P6" t="n">
-        <v>304.0028991662632</v>
+        <v>304.0218179776708</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36595,28 +36665,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3437187128978739</v>
+        <v>-0.3453755824830058</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3298457798519357</v>
+        <v>0.3323652685729294</v>
       </c>
       <c r="M7" t="n">
-        <v>2.859687476889466</v>
+        <v>2.861777903373513</v>
       </c>
       <c r="N7" t="n">
-        <v>13.83393678589309</v>
+        <v>13.84266080659975</v>
       </c>
       <c r="O7" t="n">
-        <v>3.719400057252928</v>
+        <v>3.720572644983531</v>
       </c>
       <c r="P7" t="n">
-        <v>303.3356690508157</v>
+        <v>303.3534727168016</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36673,28 +36743,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.458162763464345</v>
+        <v>-0.4594917347523111</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4110264204342098</v>
+        <v>0.4131641273177244</v>
       </c>
       <c r="M8" t="n">
-        <v>3.195992039481978</v>
+        <v>3.195610345923475</v>
       </c>
       <c r="N8" t="n">
-        <v>17.33569518376168</v>
+        <v>17.32457080543644</v>
       </c>
       <c r="O8" t="n">
-        <v>4.163615638331867</v>
+        <v>4.162279520339358</v>
       </c>
       <c r="P8" t="n">
-        <v>301.7557676592695</v>
+        <v>301.770047938857</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36751,28 +36821,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3070686499457473</v>
+        <v>-0.3129291738977977</v>
       </c>
       <c r="J9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K9" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0157527814380769</v>
+        <v>0.0163994328578082</v>
       </c>
       <c r="M9" t="n">
-        <v>13.7703023503082</v>
+        <v>13.77231910028137</v>
       </c>
       <c r="N9" t="n">
-        <v>334.9872527107098</v>
+        <v>334.7636564911994</v>
       </c>
       <c r="O9" t="n">
-        <v>18.30265698500384</v>
+        <v>18.29654766591773</v>
       </c>
       <c r="P9" t="n">
-        <v>279.8923711804</v>
+        <v>279.955950080962</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36829,28 +36899,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3878803372205332</v>
+        <v>-0.3944120499045843</v>
       </c>
       <c r="J10" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K10" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02614799864271589</v>
+        <v>0.02708133047062411</v>
       </c>
       <c r="M10" t="n">
-        <v>13.54470245679417</v>
+        <v>13.54824996340328</v>
       </c>
       <c r="N10" t="n">
-        <v>322.9428284571266</v>
+        <v>322.8642208171585</v>
       </c>
       <c r="O10" t="n">
-        <v>17.97061013035246</v>
+        <v>17.9684228806303</v>
       </c>
       <c r="P10" t="n">
-        <v>271.5786670864645</v>
+        <v>271.6488527136173</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36907,28 +36977,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4486577435206476</v>
+        <v>-0.4546808049921763</v>
       </c>
       <c r="J11" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K11" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04078252357152712</v>
+        <v>0.04194417803778749</v>
       </c>
       <c r="M11" t="n">
-        <v>12.3571293610114</v>
+        <v>12.36351098430328</v>
       </c>
       <c r="N11" t="n">
-        <v>270.6148002110315</v>
+        <v>270.5471602034003</v>
       </c>
       <c r="O11" t="n">
-        <v>16.45037386234828</v>
+        <v>16.44831785330647</v>
       </c>
       <c r="P11" t="n">
-        <v>273.1020285928259</v>
+        <v>273.1672853574183</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36985,28 +37055,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5853929538811831</v>
+        <v>-0.5864421335879404</v>
       </c>
       <c r="J12" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K12" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1689483036370925</v>
+        <v>0.1700472204179251</v>
       </c>
       <c r="M12" t="n">
-        <v>7.247020923871368</v>
+        <v>7.239104426677478</v>
       </c>
       <c r="N12" t="n">
-        <v>97.15044506974547</v>
+        <v>96.97219063560034</v>
       </c>
       <c r="O12" t="n">
-        <v>9.856492533845165</v>
+        <v>9.84744589401741</v>
       </c>
       <c r="P12" t="n">
-        <v>278.8603174583205</v>
+        <v>278.8715912756602</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37063,28 +37133,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2673119253178646</v>
+        <v>-0.2687305744771117</v>
       </c>
       <c r="J13" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K13" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06734530694159535</v>
+        <v>0.06826147790238202</v>
       </c>
       <c r="M13" t="n">
-        <v>5.815074934460431</v>
+        <v>5.811039867761101</v>
       </c>
       <c r="N13" t="n">
-        <v>57.03294784478534</v>
+        <v>56.94630577205604</v>
       </c>
       <c r="O13" t="n">
-        <v>7.552016144367366</v>
+        <v>7.546277610322591</v>
       </c>
       <c r="P13" t="n">
-        <v>271.8883747329937</v>
+        <v>271.9036186339074</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37141,28 +37211,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07913300167039257</v>
+        <v>0.07867708188297791</v>
       </c>
       <c r="J14" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K14" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006460093837905467</v>
+        <v>0.006413849266306282</v>
       </c>
       <c r="M14" t="n">
-        <v>5.898603660001351</v>
+        <v>5.889260927706481</v>
       </c>
       <c r="N14" t="n">
-        <v>55.50567349454806</v>
+        <v>55.39828209173156</v>
       </c>
       <c r="O14" t="n">
-        <v>7.45021298316686</v>
+        <v>7.443002223009984</v>
       </c>
       <c r="P14" t="n">
-        <v>265.9361717903228</v>
+        <v>265.9410708141713</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37219,28 +37289,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3813573965983865</v>
+        <v>0.3814905852902983</v>
       </c>
       <c r="J15" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K15" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1303653322101145</v>
+        <v>0.1309410875622093</v>
       </c>
       <c r="M15" t="n">
-        <v>5.721067686834869</v>
+        <v>5.710352619616483</v>
       </c>
       <c r="N15" t="n">
-        <v>55.91324339174027</v>
+        <v>55.80253815742178</v>
       </c>
       <c r="O15" t="n">
-        <v>7.477515857003599</v>
+        <v>7.470109648286415</v>
       </c>
       <c r="P15" t="n">
-        <v>263.8640631598206</v>
+        <v>263.8626319989102</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37297,28 +37367,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4316531063866372</v>
+        <v>0.4329162555537278</v>
       </c>
       <c r="J16" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K16" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L16" t="n">
-        <v>0.137236405679954</v>
+        <v>0.1384136327476549</v>
       </c>
       <c r="M16" t="n">
-        <v>6.485668225937436</v>
+        <v>6.477934232644474</v>
       </c>
       <c r="N16" t="n">
-        <v>67.50995610681726</v>
+        <v>67.397031466577</v>
       </c>
       <c r="O16" t="n">
-        <v>8.216444249601969</v>
+        <v>8.209569505557342</v>
       </c>
       <c r="P16" t="n">
-        <v>276.862971063745</v>
+        <v>276.8493980667735</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37375,28 +37445,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3223641553651465</v>
+        <v>0.322562303733429</v>
       </c>
       <c r="J17" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K17" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08909162751935218</v>
+        <v>0.08954675966615833</v>
       </c>
       <c r="M17" t="n">
-        <v>6.438161816282182</v>
+        <v>6.426347436544475</v>
       </c>
       <c r="N17" t="n">
-        <v>61.23601208680635</v>
+        <v>61.11502940819745</v>
       </c>
       <c r="O17" t="n">
-        <v>7.825344215228258</v>
+        <v>7.817610210812346</v>
       </c>
       <c r="P17" t="n">
-        <v>286.3864852698683</v>
+        <v>286.3843560936215</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37434,7 +37504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R504"/>
+  <dimension ref="A1:R505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83765,6 +83835,98 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:21:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-46.60072839893984,168.82114785892068</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-46.600323701047714,168.82045740548784</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-46.6001278849945,168.81957670592882</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-46.599852593626714,168.81876838828563</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-46.59950551648709,168.81802545115417</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-46.59918614647317,168.8172572770885</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-46.59884827713849,168.816505951067</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-46.59831652410304,168.81593121672879</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-46.59791326418581,168.81523944871142</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-46.59761459388977,168.814452417426</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>-46.59741830426303,168.81357213223248</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>-46.59711498644526,168.8127893297367</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>-46.59685147762638,168.81197026525297</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>-46.596600983089864,168.8111393440672</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>-46.59642378911212,168.81024165218597</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>-46.596144059921905,168.8094373544796</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
